--- a/order_generation/PO_excel_export/test1-1.xlsx
+++ b/order_generation/PO_excel_export/test1-1.xlsx
@@ -350,7 +350,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1266825" cy="1266825"/>
+    <ext cx="914400" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -358,6 +358,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1266825" cy="1266825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -787,7 +812,7 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>+86-574-27889688</t>
+          <t>18067420259</t>
         </is>
       </c>
       <c r="C4" s="16" t="n"/>
@@ -800,7 +825,7 @@
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>2025年11月04日</t>
+          <t>2025年12月30日</t>
         </is>
       </c>
       <c r="H4" s="16" t="n"/>
@@ -826,7 +851,7 @@
       </c>
       <c r="G5" s="18" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>郑遥杰</t>
         </is>
       </c>
       <c r="H5" s="16" t="n"/>
@@ -872,20 +897,22 @@
     <row r="7" ht="100" customFormat="1" customHeight="1" s="2">
       <c r="A7" s="29" t="inlineStr">
         <is>
-          <t>Elasticbrush01</t>
+          <t>EEHB-NBB</t>
         </is>
       </c>
       <c r="B7" s="29" t="n"/>
       <c r="C7" s="29" t="inlineStr">
         <is>
-          <t>梳身半降解材料（用新材料防断裂）加麦秸秆5645 C绿色，尼龙丝0.8mm7529U灰色尼龙丝颜色同beter，棕色 ecoed logo颜色同beter！染头颜色同梳体. 包装方式：白卡盒，卡盒我司供，箱规120/24</t>
+          <t>手柄表面电镀处理尽量光亮，黑色手柄做防静电处理。
+气垫颜色（打样确认色），植猪鬃毛，梳针颜色黑色防静电，植0.8 mm细尼龙针染头和梳针颜色一致，染头尽量偏小（视觉效果染头和梳针一体）梳针做防静电处理。
+LOGO：ellen evyse 颜色印金</t>
         </is>
       </c>
       <c r="D7" s="29" t="n">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>3.85</v>
+        <v>12.89</v>
       </c>
       <c r="F7" s="29">
         <f>D7*E7</f>
@@ -893,19 +920,34 @@
       </c>
       <c r="G7" s="29" t="inlineStr">
         <is>
-          <t>白卡盒，卡盒我司供，箱规120/24</t>
+          <t>我司提供包装，瑾秀包装，分两次发货</t>
         </is>
       </c>
       <c r="H7" s="20" t="n"/>
     </row>
-    <row r="8" ht="100.15" customFormat="1" customHeight="1" s="2">
-      <c r="A8" s="29" t="n"/>
+    <row r="8" ht="100" customFormat="1" customHeight="1" s="2">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>EEHB-NBB-4</t>
+        </is>
+      </c>
       <c r="B8" s="29" t="n"/>
-      <c r="C8" s="29" t="n"/>
-      <c r="D8" s="29" t="n"/>
-      <c r="E8" s="29" t="n"/>
-      <c r="F8" s="29" t="n"/>
-      <c r="G8" s="29" t="n"/>
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>清洁刷，注塑体黑色，植毛黑色尼龙毛，0.7mm直径，长度25mm，定制Norsewood滑块logo，产品做哑光，logo处做亮光。需打样再做货</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F8" s="29">
+        <f>D8*E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="29" t="inlineStr"/>
       <c r="H8" s="20" t="n"/>
     </row>
     <row r="9" ht="100.15" customFormat="1" customHeight="1" s="2">
@@ -954,11 +996,7 @@
           <t>进仓地址：</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
-        <is>
-          <t>浙江宁波市余姚市陆埠镇五马工业区创利西路15号</t>
-        </is>
-      </c>
+      <c r="B12" s="25" t="inlineStr"/>
       <c r="C12" s="25" t="n"/>
       <c r="D12" s="25" t="n"/>
       <c r="E12" s="25" t="n"/>
@@ -972,11 +1010,7 @@
           <t>付款方式:</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
-        <is>
-          <t>凭发票，出货45天付款，含税含运含进仓</t>
-        </is>
-      </c>
+      <c r="B13" s="25" t="inlineStr"/>
       <c r="C13" s="25" t="n"/>
       <c r="D13" s="25" t="n"/>
       <c r="E13" s="25" t="n"/>
@@ -1000,7 +1034,7 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>2025年12月19日</t>
+          <t>2031年07月23日</t>
         </is>
       </c>
       <c r="C14" s="25" t="n"/>
@@ -1016,11 +1050,7 @@
           <t>箱规:</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
-        <is>
-          <t>箱规120/24</t>
-        </is>
-      </c>
+      <c r="B15" s="25" t="inlineStr"/>
       <c r="C15" s="25" t="n"/>
       <c r="D15" s="25" t="n"/>
       <c r="E15" s="25" t="n"/>
@@ -1073,7 +1103,7 @@
     <row r="19" ht="17.25" customFormat="1" customHeight="1" s="4">
       <c r="A19" s="25" t="inlineStr">
         <is>
-          <t>快速弯折120度，快速旋转120度不得断裂（20个样品最多一个）</t>
+          <t>表面处理干净光滑，不能有划痕，做大货前先确认大货样</t>
         </is>
       </c>
       <c r="B19" s="25" t="n"/>
@@ -1085,11 +1115,7 @@
       <c r="H19" s="25" t="n"/>
     </row>
     <row r="20" ht="17.25" customFormat="1" customHeight="1" s="4">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>注意柄部干净整洁，logo处清洁摸上去没有油</t>
-        </is>
-      </c>
+      <c r="A20" s="25" t="inlineStr"/>
       <c r="B20" s="25" t="n"/>
       <c r="C20" s="25" t="n"/>
       <c r="D20" s="25" t="n"/>
@@ -1099,11 +1125,7 @@
       <c r="H20" s="25" t="n"/>
     </row>
     <row r="21" ht="17.25" customFormat="1" customHeight="1" s="4">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>外箱单边不得超过60cm，重量不得超过20公斤</t>
-        </is>
-      </c>
+      <c r="A21" s="25" t="inlineStr"/>
       <c r="B21" s="25" t="n"/>
       <c r="C21" s="25" t="n"/>
       <c r="D21" s="25" t="n"/>
@@ -1113,11 +1135,7 @@
       <c r="H21" s="25" t="n"/>
     </row>
     <row r="22" ht="17.25" customFormat="1" customHeight="1" s="4">
-      <c r="A22" s="25" t="inlineStr">
-        <is>
-          <t>尼龙丝针注意不要大量明显弯曲</t>
-        </is>
-      </c>
+      <c r="A22" s="25" t="inlineStr"/>
       <c r="B22" s="25" t="n"/>
       <c r="C22" s="25" t="n"/>
       <c r="D22" s="25" t="n"/>
@@ -1127,11 +1145,7 @@
       <c r="H22" s="25" t="n"/>
     </row>
     <row r="23" ht="17.25" customFormat="1" customHeight="1" s="4">
-      <c r="A23" s="25" t="inlineStr">
-        <is>
-          <t>染头不能有坑(2个以上），（有坑一律次品）</t>
-        </is>
-      </c>
+      <c r="A23" s="25" t="inlineStr"/>
       <c r="B23" s="25" t="n"/>
       <c r="C23" s="25" t="n"/>
       <c r="D23" s="25" t="n"/>
@@ -1141,11 +1155,7 @@
       <c r="H23" s="25" t="n"/>
     </row>
     <row r="24" ht="20.45" customFormat="1" customHeight="1" s="4">
-      <c r="A24" s="25" t="inlineStr">
-        <is>
-          <t>染头不得粘连</t>
-        </is>
-      </c>
+      <c r="A24" s="25" t="inlineStr"/>
       <c r="B24" s="25" t="n"/>
       <c r="C24" s="25" t="n"/>
       <c r="D24" s="25" t="n"/>
@@ -1156,11 +1166,7 @@
       <c r="I24" s="5" t="n"/>
     </row>
     <row r="25" ht="20.45" customFormat="1" customHeight="1" s="4">
-      <c r="A25" s="25" t="inlineStr">
-        <is>
-          <t>每个外箱需要贴2个标签FBA标签一个，货代标签一个</t>
-        </is>
-      </c>
+      <c r="A25" s="25" t="inlineStr"/>
       <c r="B25" s="25" t="n"/>
       <c r="C25" s="25" t="n"/>
       <c r="D25" s="25" t="n"/>
